--- a/test_data/gp2t.xlsx
+++ b/test_data/gp2t.xlsx
@@ -13,65 +13,38 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="90">
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>D</t>
-  </si>
-  <si>
-    <t>E</t>
-  </si>
-  <si>
-    <t>F</t>
-  </si>
-  <si>
-    <t>G</t>
-  </si>
-  <si>
-    <t>H</t>
-  </si>
-  <si>
-    <t>I</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="82">
+  <si>
+    <t>Item #</t>
+  </si>
+  <si>
+    <t>*Designator</t>
+  </si>
+  <si>
+    <t>*Qty</t>
+  </si>
+  <si>
+    <t>Manufacturer</t>
+  </si>
+  <si>
+    <t>*Mfg Part #</t>
+  </si>
+  <si>
+    <t>Description / Value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">*Package/Footprint </t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Your Instructions / Notes</t>
   </si>
   <si>
     <t>xxxx xxxx xxxxx xxPCS BOM  (Sample Bill of Materials)</t>
   </si>
   <si>
-    <t>Item #</t>
-  </si>
-  <si>
-    <t>*Designator</t>
-  </si>
-  <si>
-    <t>*Qty</t>
-  </si>
-  <si>
-    <t>Manufacturer</t>
-  </si>
-  <si>
-    <t>*Mfg Part #</t>
-  </si>
-  <si>
-    <t>Description / Value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">*Package/Footprint </t>
-  </si>
-  <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>Your Instructions / Notes</t>
-  </si>
-  <si>
     <t>U1</t>
   </si>
   <si>
@@ -283,6 +256,9 @@
   </si>
   <si>
     <t>Click for Instructions on How to Create a BOM</t>
+  </si>
+  <si>
+    <t/>
   </si>
 </sst>
 </file>
@@ -691,67 +667,39 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="D2" t="s">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="D3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25"/>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F6" t="s">
-        <v>15</v>
-      </c>
-      <c r="G6" t="s">
-        <v>16</v>
-      </c>
-      <c r="H6" t="s">
-        <v>17</v>
-      </c>
-      <c r="I6" t="s">
-        <v>18</v>
-      </c>
-    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25"/>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C7">
         <v>1</v>
       </c>
       <c r="D7" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E7" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F7" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="G7" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="H7" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
@@ -759,25 +707,25 @@
         <v>2</v>
       </c>
       <c r="B8" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="C8">
         <v>2</v>
       </c>
       <c r="D8" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="E8" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="F8" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G8" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="H8" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -785,25 +733,25 @@
         <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="C9">
         <v>1</v>
       </c>
       <c r="D9" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="E9" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F9" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="G9" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="H9" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
@@ -811,25 +759,25 @@
         <v>4</v>
       </c>
       <c r="B10" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="C10">
         <v>1</v>
       </c>
       <c r="D10" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="E10" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="F10" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="G10" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="H10" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
@@ -837,25 +785,25 @@
         <v>5</v>
       </c>
       <c r="B11" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="C11">
         <v>1</v>
       </c>
       <c r="D11" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="E11" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="F11" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="G11" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="H11" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
@@ -863,25 +811,25 @@
         <v>6</v>
       </c>
       <c r="B12" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="C12">
         <v>2</v>
       </c>
       <c r="D12" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="E12" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="F12" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="G12" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="H12" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
@@ -889,25 +837,25 @@
         <v>7</v>
       </c>
       <c r="B13" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="C13">
         <v>1</v>
       </c>
       <c r="D13" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="E13" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="F13" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="G13" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="H13" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
@@ -915,25 +863,25 @@
         <v>8</v>
       </c>
       <c r="B14" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="C14">
         <v>2</v>
       </c>
       <c r="D14" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="E14" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="F14" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="G14" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="H14" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
@@ -941,25 +889,25 @@
         <v>9</v>
       </c>
       <c r="B15" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="C15">
         <v>1</v>
       </c>
       <c r="D15" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="E15" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="F15" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="G15" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="H15" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
@@ -967,25 +915,25 @@
         <v>10</v>
       </c>
       <c r="B16" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="C16">
         <v>1</v>
       </c>
       <c r="D16" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="E16" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="F16" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="G16" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="H16" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
@@ -993,25 +941,25 @@
         <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="C17">
         <v>2</v>
       </c>
       <c r="D17" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="E17" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="F17" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="G17" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="H17" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
@@ -1019,25 +967,25 @@
         <v>12</v>
       </c>
       <c r="B18" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="C18">
         <v>1</v>
       </c>
       <c r="D18" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="E18" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F18" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="G18" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="H18" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
@@ -1045,25 +993,25 @@
         <v>13</v>
       </c>
       <c r="B19" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="C19">
         <v>2</v>
       </c>
       <c r="D19" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="E19" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="F19" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="G19" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="H19" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
@@ -1071,25 +1019,25 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="C20">
         <v>1</v>
       </c>
       <c r="D20" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="E20" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="F20" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="G20" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="H20" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
@@ -1097,38 +1045,38 @@
         <v>15</v>
       </c>
       <c r="B21" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="C21">
         <v>2</v>
       </c>
       <c r="D21" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="E21" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="F21" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G21" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H21" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25"/>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25"/>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25"/>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -1141,7 +1089,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -1151,7 +1105,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/test_data/gp2t.xlsx
+++ b/test_data/gp2t.xlsx
@@ -1066,7 +1066,11 @@
         <v>78</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>1</v>
+      </c>
+    </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25"/>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">

--- a/test_data/gp2t.xlsx
+++ b/test_data/gp2t.xlsx
@@ -1066,11 +1066,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22">
-        <v>1</v>
-      </c>
-    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25"/>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25"/>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
